--- a/ImportExportExcellApi/Templates/Employee_Template_Base.xlsx
+++ b/ImportExportExcellApi/Templates/Employee_Template_Base.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8280"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="43">
   <si>
     <t>DANH SÁCH BẰNG CẤP/CHỨNG CHỈ NHÂN VIÊN</t>
   </si>
@@ -45,6 +45,9 @@
   </si>
   <si>
     <t>NAME</t>
+  </si>
+  <si>
+    <t>GRADUATE_SCHOOL</t>
   </si>
   <si>
     <t>LEVEL_ID</t>
@@ -774,15 +777,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1335,227 +1335,226 @@
   <cols>
     <col min="1" max="2" width="20.712962962963" style="1" customWidth="1"/>
     <col min="3" max="3" width="25.712962962963" style="1" customWidth="1"/>
-    <col min="4" max="4" width="20.712962962963" style="1" customWidth="1"/>
-    <col min="5" max="5" width="25.712962962963" style="2" customWidth="1"/>
-    <col min="6" max="18" width="20.712962962963" style="1" customWidth="1"/>
+    <col min="4" max="18" width="20.712962962963" style="1" customWidth="1"/>
     <col min="19" max="16384" width="9.13888888888889" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
     </row>
     <row r="2" spans="1:20">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3"/>
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
     </row>
     <row r="3" ht="20" hidden="1" customHeight="1" spans="1:18">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="4"/>
-      <c r="G3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="H3" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="I3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="J3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="L3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="M3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="N3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="O3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q3" s="4" t="s">
+      <c r="P3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="3" t="s">
+      <c r="Q3" s="3" t="s">
         <v>17</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="4" ht="39" customHeight="1" spans="1:18">
-      <c r="A4" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="A4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="D4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="E4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="F4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="H4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="I4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="K4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="L4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="M4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="N4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="P4" s="3" t="s">
+      <c r="O4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="Q4" s="3" t="s">
+      <c r="P4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="R4" s="3" t="s">
+      <c r="Q4" s="2" t="s">
         <v>35</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:18">
-      <c r="A5" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>37</v>
       </c>
+      <c r="B5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>38</v>
+      </c>
       <c r="E5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="G5" s="3" t="s">
+      <c r="H5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="K5" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="M5" s="4" t="s">
+      <c r="L5" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="N5" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="O5" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="P5" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q5" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="R5" s="4" t="s">
-        <v>38</v>
+      <c r="M5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="R5" s="3" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="E3:F3"/>
+  <mergeCells count="1">
     <mergeCell ref="A1:T2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
